--- a/js-scripts/hardhat/tgUSD/data/routes.xlsx
+++ b/js-scripts/hardhat/tgUSD/data/routes.xlsx
@@ -8,14 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Yann\Documents\sources\convergence\tangent-contracts\js-scripts\hardhat\tgUSD\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{941E05C6-CD9B-4F9E-8B16-7F56F247085C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{632EF530-CF40-4B75-AD9A-B55089425028}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E9F601F2-9AED-49E3-BCCB-577F36FB7360}"/>
   </bookViews>
   <sheets>
     <sheet name="routes" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -42,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="64">
   <si>
     <t xml:space="preserve">START </t>
   </si>
@@ -240,7 +253,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -371,6 +384,12 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -723,10 +742,12 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="14" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20 % - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -772,17 +793,7 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Vérification" xfId="13" builtinId="23" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -1123,7 +1134,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF675477-6C4C-45A7-BD77-13FFDC2DA2A5}">
-  <dimension ref="A1:N51"/>
+  <dimension ref="A1:W51"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" bestFit="1" customWidth="1"/>
@@ -2109,7 +2120,7 @@
         <v>tgUSD*</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>41</v>
       </c>
@@ -2133,7 +2144,7 @@
         <v>tgUSD*</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>41</v>
       </c>
@@ -2169,49 +2180,42 @@
         <v>tgUSD*</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>41</v>
-      </c>
-      <c r="B35" t="s">
-        <v>17</v>
-      </c>
-      <c r="C35" t="s">
-        <v>16</v>
-      </c>
-      <c r="D35" t="s">
-        <v>9</v>
-      </c>
-      <c r="E35" t="s">
-        <v>20</v>
-      </c>
-      <c r="F35" t="s">
-        <v>21</v>
-      </c>
-      <c r="G35" t="s">
-        <v>22</v>
-      </c>
-      <c r="H35" t="s">
-        <v>23</v>
-      </c>
-      <c r="I35" t="s">
-        <v>60</v>
-      </c>
-      <c r="J35" t="s">
-        <v>60</v>
-      </c>
-      <c r="K35" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="L35" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="N35" t="str" cm="1">
-        <f t="array" ref="N35">INDEX(D35:M35, MAX(IF(D35:M35&lt;&gt;"", COLUMN(D35:M35)-COLUMN(D35)+1)))</f>
-        <v>tgUSD*</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="K35" s="2"/>
+      <c r="L35" s="2"/>
+      <c r="N35" cm="1">
+        <f t="array" ref="N35:W35">INDEX(D35:M35, MAX(IF(D35:M35&lt;&gt;"", COLUMN(D35:M35)-COLUMN(D35)+1)))</f>
+        <v>0</v>
+      </c>
+      <c r="O35">
+        <v>0</v>
+      </c>
+      <c r="P35">
+        <v>0</v>
+      </c>
+      <c r="Q35">
+        <v>0</v>
+      </c>
+      <c r="R35">
+        <v>0</v>
+      </c>
+      <c r="S35">
+        <v>0</v>
+      </c>
+      <c r="T35">
+        <v>0</v>
+      </c>
+      <c r="U35">
+        <v>0</v>
+      </c>
+      <c r="V35">
+        <v>0</v>
+      </c>
+      <c r="W35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>42</v>
       </c>
@@ -2235,7 +2239,7 @@
         <v>tgUSD*</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>42</v>
       </c>
@@ -2271,7 +2275,7 @@
         <v>tgUSD*</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>42</v>
       </c>
@@ -2301,7 +2305,7 @@
         <v>tgUSD*</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>42</v>
       </c>
@@ -2337,7 +2341,7 @@
         <v>tgUSD*</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>42</v>
       </c>
@@ -2361,7 +2365,7 @@
         <v>tgUSD*</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>42</v>
       </c>
@@ -2385,7 +2389,7 @@
         <v>tgUSD*</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>35</v>
       </c>
@@ -2409,7 +2413,7 @@
         <v>tgUSD*</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>35</v>
       </c>
@@ -2433,7 +2437,7 @@
         <v>tgUSD*</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>35</v>
       </c>
@@ -2469,7 +2473,7 @@
         <v>tgUSD*</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>35</v>
       </c>
@@ -2493,29 +2497,35 @@
         <v>tgUSD*</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
+    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A46" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C46" t="s">
+      <c r="C46" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D46" t="s">
+      <c r="D46" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E46" t="s">
+      <c r="E46" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G46" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="F46" t="s">
+      <c r="H46" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="G46" t="s">
+      <c r="I46" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="H46" t="s">
+      <c r="J46" s="4" t="s">
         <v>53</v>
       </c>
       <c r="N46" t="str" cm="1">
@@ -2523,7 +2533,7 @@
         <v>tgUSD*</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>35</v>
       </c>
@@ -2559,35 +2569,29 @@
         <v>tgUSD*</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>33</v>
       </c>
       <c r="B48" t="s">
         <v>31</v>
       </c>
-      <c r="C48" t="s">
-        <v>31</v>
-      </c>
-      <c r="D48" t="s">
-        <v>19</v>
+      <c r="C48" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>13</v>
       </c>
       <c r="E48" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="F48" t="s">
-        <v>13</v>
+        <v>51</v>
       </c>
       <c r="G48" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H48" t="s">
-        <v>51</v>
-      </c>
-      <c r="I48" t="s">
-        <v>52</v>
-      </c>
-      <c r="J48" t="s">
         <v>53</v>
       </c>
       <c r="N48" t="str" cm="1">
@@ -2626,34 +2630,16 @@
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>33</v>
-      </c>
-      <c r="B50" t="s">
-        <v>31</v>
-      </c>
-      <c r="C50" t="s">
-        <v>31</v>
-      </c>
-      <c r="D50" t="s">
-        <v>19</v>
-      </c>
-      <c r="E50" t="s">
-        <v>56</v>
-      </c>
-      <c r="F50" t="s">
-        <v>56</v>
-      </c>
-      <c r="G50" t="s">
-        <v>59</v>
-      </c>
-      <c r="H50" t="s">
-        <v>53</v>
-      </c>
-      <c r="N50" t="str" cm="1">
-        <f t="array" ref="N50">INDEX(D50:M50, MAX(IF(D50:M50&lt;&gt;"", COLUMN(D50:M50)-COLUMN(D50)+1)))</f>
-        <v>tgUSD*</v>
-      </c>
+      <c r="A50" s="4"/>
+      <c r="B50" s="4"/>
+      <c r="C50" s="4"/>
+      <c r="D50" s="4"/>
+      <c r="E50" s="4"/>
+      <c r="F50" s="4"/>
+      <c r="G50" s="4"/>
+      <c r="H50" s="4"/>
+      <c r="I50" s="3"/>
+      <c r="J50" s="3"/>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
